--- a/organisatorisches/Arbeitszeitererfassung.xlsx
+++ b/organisatorisches/Arbeitszeitererfassung.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Schule\3-Klasse\MuscleOn\organisatorisches\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Schule\3-Klasse\MuscleOn\MuscleOn-Project\organisatorisches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89620482-4FE2-40D4-A2BA-18E844F42038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B90E5F47-A514-46F4-AF81-F73824F5024A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1110" yWindow="3000" windowWidth="19200" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="770" yWindow="2660" windowWidth="19200" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tobias" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="17">
   <si>
     <t>Datum</t>
   </si>
@@ -86,6 +86,9 @@
   </si>
   <si>
     <t>Website Layout design im CSS</t>
+  </si>
+  <si>
+    <t>Website Color design im CSS</t>
   </si>
 </sst>
 </file>
@@ -817,7 +820,7 @@
         <v>1.0416666666666666E-2</v>
       </c>
       <c r="E3" s="7">
-        <f t="shared" ref="E3:E5" si="0">IF(C3-B3-IF(ISNUMBER(D3), D3, 0) &lt;&gt; 0, C3-B3-IF(ISNUMBER(D3), D3, 0), "")</f>
+        <f t="shared" ref="E3" si="0">IF(C3-B3-IF(ISNUMBER(D3), D3, 0) &lt;&gt; 0, C3-B3-IF(ISNUMBER(D3), D3, 0), "")</f>
         <v>6.9444444444444434E-2</v>
       </c>
       <c r="F3" t="s">
@@ -846,13 +849,22 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="3"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="2"/>
+      <c r="A5" s="4">
+        <v>45974</v>
+      </c>
+      <c r="B5" s="5">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.40625</v>
+      </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="7" t="str">
+      <c r="E5" s="7">
         <f t="shared" si="1"/>
-        <v/>
+        <v>7.2916666666666685E-2</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -861,7 +873,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="3"/>
       <c r="E6" s="7" t="str">
-        <f t="shared" ref="E3:E20" si="2">IF(C6-B6-IF(ISNUMBER(D6), D6, 0) &lt;&gt; 0, C6-B6-IF(ISNUMBER(D6), D6, 0), "")</f>
+        <f t="shared" ref="E6:E20" si="2">IF(C6-B6-IF(ISNUMBER(D6), D6, 0) &lt;&gt; 0, C6-B6-IF(ISNUMBER(D6), D6, 0), "")</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1026,7 @@
       <c r="D21" s="10"/>
       <c r="E21" s="8">
         <f>SUM(E2:E20)</f>
-        <v>0.21527777777777779</v>
+        <v>0.28819444444444448</v>
       </c>
     </row>
   </sheetData>
